--- a/2026秋学期工程训练_0308.xlsx
+++ b/2026秋学期工程训练_0308.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mac/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hhhyc\Desktop\新建文件夹 (6)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18D8317B-8F18-7347-967E-6EC7E6BD33F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F43AAA7-0BB7-41BB-AD4B-976AA752D4A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="20220" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="550" yWindow="360" windowWidth="36750" windowHeight="20440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="排课表" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">排课表!$A$1:$W$177</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -24,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="290">
   <si>
     <t>星期</t>
   </si>
@@ -281,16 +283,10 @@
 A智5-7</t>
   </si>
   <si>
-    <t>机械设计制造及其自动化(国际综合1班)国际26+（一体化）14人</t>
-  </si>
-  <si>
     <t>B激1-4
 A热1-4
 B压5-7
 A焊5-7</t>
-  </si>
-  <si>
-    <t>机械设计制造及其自动化(国际综合2班)中德26+（一体化）14人</t>
   </si>
   <si>
     <t>B压1-4
@@ -729,15 +725,6 @@
 B产5-7</t>
   </si>
   <si>
-    <t>铸1-4
-铣m5-7</t>
-  </si>
-  <si>
-    <t>B智1-4
-A产1-4
-数x5-7</t>
-  </si>
-  <si>
     <t>车1-4
 焊5-7</t>
   </si>
@@ -1122,10 +1109,6 @@
 B热5-7</t>
   </si>
   <si>
-    <t>机械设计制造及其自动化国际综合项目1-4
-机械设计制造及其自动化国际综合项目5-7</t>
-  </si>
-  <si>
     <t>A装1-4
 B五1-4
 B柔5-7
@@ -1136,13 +1119,6 @@
 A机1-4
 A装5-7
 B五5-7</t>
-  </si>
-  <si>
-    <t>A超1-2
-B齿1-2
-B超3-4
-A齿3-4
-铣m5-7</t>
   </si>
   <si>
     <t>B热1-4
@@ -1236,12 +1212,84 @@
 数c5-7</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>机械设计制造及其自动化项目1-4
+机械设计制造及其自动化项目5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A超1-2
+B齿1-2
+B超3-4
+A齿3-4
+机械设计制造及其自动化项目5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化(国际综合1班)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>机械设计制造及其自动化(国际综合2班)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>先d1-4
+钳5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>钳1-4
+先d5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>理论1-4
+智能制造工程项目5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能制造工程项目1-4
+A压5-7
+B焊5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>智能制造工程项目1-4
+A激5-7
+B热5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>焊5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B智5-7
+A产5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铣m1-4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>铸1-4
+先d5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B智1-4
+A产1-4
+数x5-7</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1310,7 +1358,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1337,6 +1385,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1642,7 +1693,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X177"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -1650,7 +1701,7 @@
     <col min="24" max="24" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="30">
+    <row r="1" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1722,7 +1773,7 @@
       </c>
       <c r="X1" s="1"/>
     </row>
-    <row r="2" spans="1:24" ht="75">
+    <row r="2" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1758,7 +1809,7 @@
       <c r="W2" s="1"/>
       <c r="X2" s="2"/>
     </row>
-    <row r="3" spans="1:24" ht="75">
+    <row r="3" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
@@ -1794,7 +1845,7 @@
       <c r="W3" s="1"/>
       <c r="X3" s="2"/>
     </row>
-    <row r="4" spans="1:24" ht="75">
+    <row r="4" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
@@ -1811,8 +1862,8 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="1" t="s">
-        <v>33</v>
+      <c r="M4" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="N4" s="1" t="s">
         <v>34</v>
@@ -1830,7 +1881,7 @@
       <c r="W4" s="1"/>
       <c r="X4" s="2"/>
     </row>
-    <row r="5" spans="1:24" ht="75">
+    <row r="5" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>23</v>
       </c>
@@ -1847,8 +1898,8 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
-      <c r="M5" s="1" t="s">
-        <v>37</v>
+      <c r="M5" s="5" t="s">
+        <v>282</v>
       </c>
       <c r="N5" s="1" t="s">
         <v>38</v>
@@ -1866,7 +1917,7 @@
       <c r="W5" s="1"/>
       <c r="X5" s="2"/>
     </row>
-    <row r="6" spans="1:24" ht="45">
+    <row r="6" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>23</v>
       </c>
@@ -1890,19 +1941,19 @@
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
       <c r="S6" s="9" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="U6" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="2"/>
     </row>
-    <row r="7" spans="1:24" ht="75">
+    <row r="7" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
@@ -1926,7 +1977,7 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="5" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="T7" s="1" t="s">
         <v>31</v>
@@ -1938,7 +1989,7 @@
       <c r="W7" s="1"/>
       <c r="X7" s="2"/>
     </row>
-    <row r="8" spans="1:24" ht="75">
+    <row r="8" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>23</v>
       </c>
@@ -1974,7 +2025,7 @@
       <c r="W8" s="1"/>
       <c r="X8" s="2"/>
     </row>
-    <row r="9" spans="1:24" ht="105">
+    <row r="9" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>23</v>
       </c>
@@ -2001,7 +2052,7 @@
         <v>48</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>50</v>
@@ -2010,7 +2061,7 @@
       <c r="W9" s="1"/>
       <c r="X9" s="2"/>
     </row>
-    <row r="10" spans="1:24" ht="75">
+    <row r="10" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>23</v>
       </c>
@@ -2046,7 +2097,7 @@
       <c r="W10" s="1"/>
       <c r="X10" s="2"/>
     </row>
-    <row r="11" spans="1:24" ht="45">
+    <row r="11" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -2082,7 +2133,7 @@
       <c r="W11" s="1"/>
       <c r="X11" s="2"/>
     </row>
-    <row r="12" spans="1:24" ht="75">
+    <row r="12" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -2109,7 +2160,7 @@
         <v>37</v>
       </c>
       <c r="T12" s="5" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="U12" s="1" t="s">
         <v>58</v>
@@ -2118,12 +2169,12 @@
       <c r="W12" s="1"/>
       <c r="X12" s="2"/>
     </row>
-    <row r="13" spans="1:24" ht="75">
+    <row r="13" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>59</v>
+      <c r="B13" s="5" t="s">
+        <v>278</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2132,7 +2183,7 @@
         <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -2154,12 +2205,12 @@
       <c r="W13" s="1"/>
       <c r="X13" s="2"/>
     </row>
-    <row r="14" spans="1:24" ht="75">
+    <row r="14" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>61</v>
+      <c r="B14" s="5" t="s">
+        <v>279</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>48</v>
@@ -2168,7 +2219,7 @@
         <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -2190,12 +2241,12 @@
       <c r="W14" s="1"/>
       <c r="X14" s="2"/>
     </row>
-    <row r="15" spans="1:24" ht="75">
+    <row r="15" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
@@ -2217,7 +2268,7 @@
         <v>34</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="S15" s="1"/>
       <c r="T15" s="1"/>
@@ -2226,12 +2277,12 @@
       <c r="W15" s="1"/>
       <c r="X15" s="2"/>
     </row>
-    <row r="16" spans="1:24" ht="75">
+    <row r="16" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
@@ -2253,7 +2304,7 @@
         <v>45</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
@@ -2262,12 +2313,12 @@
       <c r="W16" s="1"/>
       <c r="X16" s="2"/>
     </row>
-    <row r="17" spans="1:24" ht="75">
+    <row r="17" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
@@ -2298,12 +2349,12 @@
       <c r="W17" s="1"/>
       <c r="X17" s="2"/>
     </row>
-    <row r="18" spans="1:24" ht="75">
+    <row r="18" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
@@ -2334,12 +2385,12 @@
       <c r="W18" s="1"/>
       <c r="X18" s="2"/>
     </row>
-    <row r="19" spans="1:24" ht="60">
+    <row r="19" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
@@ -2361,7 +2412,7 @@
         <v>38</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
@@ -2370,12 +2421,12 @@
       <c r="W19" s="1"/>
       <c r="X19" s="2"/>
     </row>
-    <row r="20" spans="1:24" ht="90">
+    <row r="20" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
@@ -2391,13 +2442,13 @@
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
@@ -2406,41 +2457,41 @@
       <c r="W20" s="1"/>
       <c r="X20" s="2"/>
     </row>
-    <row r="21" spans="1:24" ht="60">
+    <row r="21" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>56</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="N21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
@@ -2452,38 +2503,38 @@
       <c r="W21" s="1"/>
       <c r="X21" s="2"/>
     </row>
-    <row r="22" spans="1:24" ht="60">
+    <row r="22" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="M22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>81</v>
-      </c>
       <c r="N22" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>56</v>
@@ -2498,12 +2549,12 @@
       <c r="W22" s="1"/>
       <c r="X22" s="2"/>
     </row>
-    <row r="23" spans="1:24" ht="60">
+    <row r="23" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
@@ -2516,20 +2567,20 @@
         <v>55</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
@@ -2540,12 +2591,12 @@
       <c r="W23" s="1"/>
       <c r="X23" s="2"/>
     </row>
-    <row r="24" spans="1:24" ht="60">
+    <row r="24" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
@@ -2558,20 +2609,20 @@
         <v>55</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L24" s="1"/>
       <c r="M24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="P24" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
@@ -2582,37 +2633,37 @@
       <c r="W24" s="1"/>
       <c r="X24" s="2"/>
     </row>
-    <row r="25" spans="1:24" ht="60">
+    <row r="25" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="F25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="s">
         <v>56</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
@@ -2628,12 +2679,12 @@
       <c r="W25" s="1"/>
       <c r="X25" s="2"/>
     </row>
-    <row r="26" spans="1:24" ht="60">
+    <row r="26" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
@@ -2646,19 +2697,19 @@
         <v>55</v>
       </c>
       <c r="K26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="M26" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="N26" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="O26" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
@@ -2670,31 +2721,31 @@
       <c r="W26" s="1"/>
       <c r="X26" s="2"/>
     </row>
-    <row r="27" spans="1:24" ht="60">
+    <row r="27" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
@@ -2712,31 +2763,31 @@
       <c r="W27" s="1"/>
       <c r="X27" s="2"/>
     </row>
-    <row r="28" spans="1:24" ht="60">
+    <row r="28" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
@@ -2754,37 +2805,37 @@
       <c r="W28" s="1"/>
       <c r="X28" s="2"/>
     </row>
-    <row r="29" spans="1:24" ht="60">
+    <row r="29" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -2800,34 +2851,34 @@
       <c r="W29" s="1"/>
       <c r="X29" s="2"/>
     </row>
-    <row r="30" spans="1:24" ht="60">
+    <row r="30" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>56</v>
@@ -2846,12 +2897,12 @@
       <c r="W30" s="1"/>
       <c r="X30" s="2"/>
     </row>
-    <row r="31" spans="1:24" ht="60">
+    <row r="31" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -2860,20 +2911,20 @@
         <v>55</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
@@ -2888,12 +2939,12 @@
       <c r="W31" s="1"/>
       <c r="X31" s="2"/>
     </row>
-    <row r="32" spans="1:24" ht="60">
+    <row r="32" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2902,20 +2953,20 @@
         <v>55</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="L32" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
@@ -2930,12 +2981,12 @@
       <c r="W32" s="1"/>
       <c r="X32" s="2"/>
     </row>
-    <row r="33" spans="1:24" ht="60">
+    <row r="33" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2944,19 +2995,19 @@
         <v>55</v>
       </c>
       <c r="G33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I33" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="J33" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="K33" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -2972,12 +3023,12 @@
       <c r="W33" s="1"/>
       <c r="X33" s="2"/>
     </row>
-    <row r="34" spans="1:24" ht="60">
+    <row r="34" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2986,19 +3037,19 @@
         <v>55</v>
       </c>
       <c r="G34" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K34" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -3014,9 +3065,9 @@
       <c r="W34" s="1"/>
       <c r="X34" s="2"/>
     </row>
-    <row r="35" spans="1:24" ht="75">
+    <row r="35" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>24</v>
@@ -3038,7 +3089,7 @@
         <v>41</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
@@ -3050,9 +3101,9 @@
       <c r="W35" s="1"/>
       <c r="X35" s="2"/>
     </row>
-    <row r="36" spans="1:24" ht="75">
+    <row r="36" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>28</v>
@@ -3074,7 +3125,7 @@
         <v>27</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
@@ -3086,9 +3137,9 @@
       <c r="W36" s="1"/>
       <c r="X36" s="2"/>
     </row>
-    <row r="37" spans="1:24" ht="75">
+    <row r="37" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>32</v>
@@ -3110,7 +3161,7 @@
         <v>38</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
@@ -3122,9 +3173,9 @@
       <c r="W37" s="1"/>
       <c r="X37" s="2"/>
     </row>
-    <row r="38" spans="1:24" ht="75">
+    <row r="38" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>36</v>
@@ -3158,9 +3209,9 @@
       <c r="W38" s="1"/>
       <c r="X38" s="2"/>
     </row>
-    <row r="39" spans="1:24" ht="45">
+    <row r="39" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>40</v>
@@ -3188,15 +3239,15 @@
         <v>45</v>
       </c>
       <c r="U39" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="V39" s="1"/>
       <c r="W39" s="1"/>
       <c r="X39" s="2"/>
     </row>
-    <row r="40" spans="1:24" ht="75">
+    <row r="40" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>42</v>
@@ -3224,15 +3275,15 @@
         <v>26</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="V40" s="1"/>
       <c r="W40" s="1"/>
       <c r="X40" s="2"/>
     </row>
-    <row r="41" spans="1:24" ht="75">
+    <row r="41" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>44</v>
@@ -3260,15 +3311,15 @@
         <v>49</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V41" s="1"/>
       <c r="W41" s="1"/>
       <c r="X41" s="2"/>
     </row>
-    <row r="42" spans="1:24" ht="75">
+    <row r="42" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>47</v>
@@ -3302,9 +3353,9 @@
       <c r="W42" s="1"/>
       <c r="X42" s="2"/>
     </row>
-    <row r="43" spans="1:24" ht="75">
+    <row r="43" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>51</v>
@@ -3332,15 +3383,15 @@
         <v>34</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="V43" s="1"/>
       <c r="W43" s="1"/>
       <c r="X43" s="2"/>
     </row>
-    <row r="44" spans="1:24" ht="105">
+    <row r="44" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>54</v>
@@ -3365,18 +3416,18 @@
         <v>45</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V44" s="1"/>
       <c r="W44" s="1"/>
       <c r="X44" s="2"/>
     </row>
-    <row r="45" spans="1:24" ht="105">
+    <row r="45" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>57</v>
@@ -3404,18 +3455,18 @@
         <v>52</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="V45" s="1"/>
       <c r="W45" s="1"/>
       <c r="X45" s="2"/>
     </row>
-    <row r="46" spans="1:24" ht="60">
+    <row r="46" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>121</v>
+        <v>102</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>278</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>41</v>
@@ -3424,7 +3475,7 @@
         <v>49</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -3446,12 +3497,12 @@
       <c r="W46" s="1"/>
       <c r="X46" s="2"/>
     </row>
-    <row r="47" spans="1:24" ht="60">
+    <row r="47" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>38</v>
@@ -3460,7 +3511,7 @@
         <v>26</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -3482,12 +3533,12 @@
       <c r="W47" s="1"/>
       <c r="X47" s="2"/>
     </row>
-    <row r="48" spans="1:24" ht="75">
+    <row r="48" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
@@ -3509,7 +3560,7 @@
         <v>52</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
@@ -3518,12 +3569,12 @@
       <c r="W48" s="1"/>
       <c r="X48" s="2"/>
     </row>
-    <row r="49" spans="1:24" ht="105">
+    <row r="49" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -3545,7 +3596,7 @@
         <v>34</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="S49" s="1"/>
       <c r="T49" s="1"/>
@@ -3554,12 +3605,12 @@
       <c r="W49" s="1"/>
       <c r="X49" s="2"/>
     </row>
-    <row r="50" spans="1:24" ht="75">
+    <row r="50" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
@@ -3581,7 +3632,7 @@
         <v>45</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="S50" s="1"/>
       <c r="T50" s="1"/>
@@ -3590,12 +3641,12 @@
       <c r="W50" s="1"/>
       <c r="X50" s="2"/>
     </row>
-    <row r="51" spans="1:24" ht="75">
+    <row r="51" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
@@ -3617,7 +3668,7 @@
         <v>49</v>
       </c>
       <c r="R51" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="S51" s="1"/>
       <c r="T51" s="1"/>
@@ -3626,12 +3677,12 @@
       <c r="W51" s="1"/>
       <c r="X51" s="2"/>
     </row>
-    <row r="52" spans="1:24" ht="75">
+    <row r="52" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
@@ -3653,7 +3704,7 @@
         <v>31</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
@@ -3662,12 +3713,12 @@
       <c r="W52" s="1"/>
       <c r="X52" s="2"/>
     </row>
-    <row r="53" spans="1:24" ht="75">
+    <row r="53" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
@@ -3689,7 +3740,7 @@
         <v>41</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
@@ -3698,36 +3749,36 @@
       <c r="W53" s="1"/>
       <c r="X53" s="2"/>
     </row>
-    <row r="54" spans="1:24" ht="60">
+    <row r="54" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="E54" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>56</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -3744,36 +3795,36 @@
       <c r="W54" s="1"/>
       <c r="X54" s="2"/>
     </row>
-    <row r="55" spans="1:24" ht="60">
+    <row r="55" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E55" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="F55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H55" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>56</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -3790,30 +3841,30 @@
       <c r="W55" s="1"/>
       <c r="X55" s="2"/>
     </row>
-    <row r="56" spans="1:24" ht="60">
+    <row r="56" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G56" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F56" s="1" t="s">
+      <c r="H56" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1"/>
@@ -3832,30 +3883,30 @@
       <c r="W56" s="1"/>
       <c r="X56" s="2"/>
     </row>
-    <row r="57" spans="1:24" ht="60">
+    <row r="57" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G57" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="H57" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
@@ -3874,12 +3925,12 @@
       <c r="W57" s="1"/>
       <c r="X57" s="2"/>
     </row>
-    <row r="58" spans="1:24" ht="60">
+    <row r="58" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
@@ -3888,19 +3939,19 @@
         <v>55</v>
       </c>
       <c r="G58" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I58" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="J58" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="K58" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3916,12 +3967,12 @@
       <c r="W58" s="1"/>
       <c r="X58" s="2"/>
     </row>
-    <row r="59" spans="1:24" ht="60">
+    <row r="59" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
@@ -3930,19 +3981,19 @@
         <v>55</v>
       </c>
       <c r="G59" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="J59" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3958,12 +4009,12 @@
       <c r="W59" s="1"/>
       <c r="X59" s="2"/>
     </row>
-    <row r="60" spans="1:24" ht="60">
+    <row r="60" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
@@ -3979,19 +4030,19 @@
         <v>55</v>
       </c>
       <c r="N60" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="P60" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="O60" s="1" t="s">
+      <c r="Q60" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="R60" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="R60" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="S60" s="1"/>
       <c r="T60" s="1"/>
@@ -4000,12 +4051,12 @@
       <c r="W60" s="1"/>
       <c r="X60" s="2"/>
     </row>
-    <row r="61" spans="1:24" ht="60">
+    <row r="61" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
@@ -4021,19 +4072,19 @@
         <v>55</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O61" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="S61" s="1"/>
       <c r="T61" s="1"/>
@@ -4042,19 +4093,19 @@
       <c r="W61" s="1"/>
       <c r="X61" s="2"/>
     </row>
-    <row r="62" spans="1:24" ht="75">
+    <row r="62" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -4074,12 +4125,12 @@
       <c r="W62" s="1"/>
       <c r="X62" s="2"/>
     </row>
-    <row r="63" spans="1:24" ht="75">
+    <row r="63" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -4088,7 +4139,7 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
@@ -4106,12 +4157,12 @@
       <c r="W63" s="1"/>
       <c r="X63" s="2"/>
     </row>
-    <row r="64" spans="1:24" ht="75">
+    <row r="64" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -4121,7 +4172,7 @@
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
       <c r="J64" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -4138,12 +4189,12 @@
       <c r="W64" s="1"/>
       <c r="X64" s="2"/>
     </row>
-    <row r="65" spans="1:24" ht="75">
+    <row r="65" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -4154,7 +4205,7 @@
       <c r="I65" s="1"/>
       <c r="J65" s="1"/>
       <c r="K65" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -4170,12 +4221,12 @@
       <c r="W65" s="1"/>
       <c r="X65" s="2"/>
     </row>
-    <row r="66" spans="1:24" ht="75">
+    <row r="66" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -4191,7 +4242,7 @@
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="Q66" s="1"/>
       <c r="R66" s="1"/>
@@ -4202,12 +4253,12 @@
       <c r="W66" s="1"/>
       <c r="X66" s="2"/>
     </row>
-    <row r="67" spans="1:24" ht="75">
+    <row r="67" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -4224,7 +4275,7 @@
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="R67" s="1"/>
       <c r="S67" s="1"/>
@@ -4234,12 +4285,12 @@
       <c r="W67" s="1"/>
       <c r="X67" s="2"/>
     </row>
-    <row r="68" spans="1:24" ht="75">
+    <row r="68" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
@@ -4257,7 +4308,7 @@
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
       <c r="R68" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="S68" s="1"/>
       <c r="T68" s="1"/>
@@ -4266,12 +4317,12 @@
       <c r="W68" s="1"/>
       <c r="X68" s="2"/>
     </row>
-    <row r="69" spans="1:24" ht="75">
+    <row r="69" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
@@ -4290,7 +4341,7 @@
       <c r="Q69" s="1"/>
       <c r="R69" s="1"/>
       <c r="S69" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="T69" s="1"/>
       <c r="U69" s="1"/>
@@ -4298,12 +4349,12 @@
       <c r="W69" s="1"/>
       <c r="X69" s="2"/>
     </row>
-    <row r="70" spans="1:24" ht="75">
+    <row r="70" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
@@ -4323,19 +4374,19 @@
       <c r="R70" s="1"/>
       <c r="S70" s="1"/>
       <c r="T70" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1"/>
       <c r="W70" s="1"/>
       <c r="X70" s="2"/>
     </row>
-    <row r="71" spans="1:24" ht="75">
+    <row r="71" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
@@ -4347,7 +4398,7 @@
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -4362,12 +4413,12 @@
       <c r="W71" s="1"/>
       <c r="X71" s="2"/>
     </row>
-    <row r="72" spans="1:24" ht="75">
+    <row r="72" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
@@ -4380,7 +4431,7 @@
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
@@ -4394,12 +4445,12 @@
       <c r="W72" s="1"/>
       <c r="X72" s="2"/>
     </row>
-    <row r="73" spans="1:24" ht="75">
+    <row r="73" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
@@ -4413,7 +4464,7 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
@@ -4426,12 +4477,12 @@
       <c r="W73" s="1"/>
       <c r="X73" s="2"/>
     </row>
-    <row r="74" spans="1:24" ht="75">
+    <row r="74" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
@@ -4446,7 +4497,7 @@
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
       <c r="O74" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1"/>
@@ -4458,12 +4509,12 @@
       <c r="W74" s="1"/>
       <c r="X74" s="2"/>
     </row>
-    <row r="75" spans="1:24" ht="75">
+    <row r="75" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
@@ -4476,7 +4527,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
@@ -4490,12 +4541,12 @@
       <c r="W75" s="1"/>
       <c r="X75" s="2"/>
     </row>
-    <row r="76" spans="1:24" ht="75">
+    <row r="76" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
@@ -4507,7 +4558,7 @@
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
@@ -4522,12 +4573,12 @@
       <c r="W76" s="1"/>
       <c r="X76" s="2"/>
     </row>
-    <row r="77" spans="1:24" ht="75">
+    <row r="77" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
@@ -4537,7 +4588,7 @@
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
       <c r="J77" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -4554,12 +4605,12 @@
       <c r="W77" s="1"/>
       <c r="X77" s="2"/>
     </row>
-    <row r="78" spans="1:24" ht="75">
+    <row r="78" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -4568,7 +4619,7 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
@@ -4586,12 +4637,12 @@
       <c r="W78" s="1"/>
       <c r="X78" s="2"/>
     </row>
-    <row r="79" spans="1:24" ht="75">
+    <row r="79" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -4605,7 +4656,7 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
       <c r="N79" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O79" s="1"/>
       <c r="P79" s="1"/>
@@ -4618,12 +4669,12 @@
       <c r="W79" s="1"/>
       <c r="X79" s="2"/>
     </row>
-    <row r="80" spans="1:24" ht="75">
+    <row r="80" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -4634,7 +4685,7 @@
       <c r="I80" s="1"/>
       <c r="J80" s="1"/>
       <c r="K80" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
@@ -4650,12 +4701,12 @@
       <c r="W80" s="1"/>
       <c r="X80" s="2"/>
     </row>
-    <row r="81" spans="1:24" ht="75">
+    <row r="81" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
@@ -4671,7 +4722,7 @@
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
       <c r="P81" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="Q81" s="4" t="s">
         <v>26</v>
@@ -4684,12 +4735,12 @@
       <c r="W81" s="1"/>
       <c r="X81" s="2"/>
     </row>
-    <row r="82" spans="1:24" ht="75">
+    <row r="82" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -4706,7 +4757,7 @@
       <c r="O82" s="1"/>
       <c r="P82" s="1"/>
       <c r="Q82" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="R82" s="4" t="s">
         <v>26</v>
@@ -4718,12 +4769,12 @@
       <c r="W82" s="1"/>
       <c r="X82" s="2"/>
     </row>
-    <row r="83" spans="1:24" ht="75">
+    <row r="83" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
@@ -4741,7 +4792,7 @@
       <c r="P83" s="1"/>
       <c r="Q83" s="1"/>
       <c r="R83" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="S83" s="4" t="s">
         <v>26</v>
@@ -4752,12 +4803,12 @@
       <c r="W83" s="1"/>
       <c r="X83" s="2"/>
     </row>
-    <row r="84" spans="1:24" ht="75">
+    <row r="84" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -4780,18 +4831,18 @@
         <v>26</v>
       </c>
       <c r="U84" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="V84" s="1"/>
       <c r="W84" s="1"/>
       <c r="X84" s="2"/>
     </row>
-    <row r="85" spans="1:24" ht="75">
+    <row r="85" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -4815,17 +4866,17 @@
         <v>26</v>
       </c>
       <c r="V85" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="W85" s="1"/>
       <c r="X85" s="2"/>
     </row>
-    <row r="86" spans="1:24" ht="75">
+    <row r="86" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -4841,7 +4892,7 @@
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
       <c r="P86" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="Q86" s="4" t="s">
         <v>26</v>
@@ -4854,12 +4905,12 @@
       <c r="W86" s="1"/>
       <c r="X86" s="2"/>
     </row>
-    <row r="87" spans="1:24" ht="75">
+    <row r="87" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
@@ -4878,7 +4929,7 @@
         <v>26</v>
       </c>
       <c r="Q87" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="R87" s="1"/>
       <c r="S87" s="1"/>
@@ -4888,12 +4939,12 @@
       <c r="W87" s="1"/>
       <c r="X87" s="2"/>
     </row>
-    <row r="88" spans="1:24" ht="75">
+    <row r="88" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
@@ -4911,7 +4962,7 @@
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="S88" s="4" t="s">
         <v>26</v>
@@ -4922,12 +4973,12 @@
       <c r="W88" s="1"/>
       <c r="X88" s="2"/>
     </row>
-    <row r="89" spans="1:24" ht="75">
+    <row r="89" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
@@ -4948,7 +4999,7 @@
         <v>26</v>
       </c>
       <c r="S89" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="T89" s="1"/>
       <c r="U89" s="1"/>
@@ -4956,12 +5007,12 @@
       <c r="W89" s="1"/>
       <c r="X89" s="2"/>
     </row>
-    <row r="90" spans="1:24" ht="75">
+    <row r="90" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
@@ -4981,7 +5032,7 @@
       <c r="R90" s="1"/>
       <c r="S90" s="1"/>
       <c r="T90" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="U90" s="4" t="s">
         <v>26</v>
@@ -4990,12 +5041,12 @@
       <c r="W90" s="1"/>
       <c r="X90" s="2"/>
     </row>
-    <row r="91" spans="1:24" ht="75">
+    <row r="91" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
@@ -5018,18 +5069,18 @@
         <v>26</v>
       </c>
       <c r="U91" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="V91" s="1"/>
       <c r="W91" s="1"/>
       <c r="X91" s="2"/>
     </row>
-    <row r="92" spans="1:24" ht="30">
+    <row r="92" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
@@ -5038,16 +5089,16 @@
         <v>55</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H92" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I92" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="I92" s="1" t="s">
+      <c r="J92" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -5064,12 +5115,12 @@
       <c r="W92" s="1"/>
       <c r="X92" s="2"/>
     </row>
-    <row r="93" spans="1:24" ht="60">
+    <row r="93" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
@@ -5078,16 +5129,16 @@
         <v>55</v>
       </c>
       <c r="G93" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I93" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="H93" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="J93" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
@@ -5104,35 +5155,37 @@
       <c r="W93" s="1"/>
       <c r="X93" s="2"/>
     </row>
-    <row r="94" spans="1:24" ht="60">
+    <row r="94" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
-      <c r="F94" s="1" t="s">
+      <c r="F94" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="G94" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="H94" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="I94" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="J94" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="K94" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L94" s="1"/>
+        <v>108</v>
+      </c>
+      <c r="L94" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
@@ -5146,36 +5199,36 @@
       <c r="W94" s="1"/>
       <c r="X94" s="2"/>
     </row>
-    <row r="95" spans="1:24" ht="60">
+    <row r="95" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
       <c r="F95" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="J95" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="K95" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H95" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I95" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="J95" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>186</v>
-      </c>
       <c r="L95" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
@@ -5190,9 +5243,9 @@
       <c r="W95" s="1"/>
       <c r="X95" s="2"/>
     </row>
-    <row r="96" spans="1:24" ht="75">
+    <row r="96" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>24</v>
@@ -5211,10 +5264,10 @@
         <v>52</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1"/>
@@ -5226,9 +5279,9 @@
       <c r="W96" s="1"/>
       <c r="X96" s="2"/>
     </row>
-    <row r="97" spans="1:24" ht="75">
+    <row r="97" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>28</v>
@@ -5250,7 +5303,7 @@
         <v>41</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1"/>
@@ -5262,9 +5315,9 @@
       <c r="W97" s="1"/>
       <c r="X97" s="2"/>
     </row>
-    <row r="98" spans="1:24" ht="60">
+    <row r="98" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>32</v>
@@ -5286,7 +5339,7 @@
         <v>45</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="1"/>
@@ -5298,9 +5351,9 @@
       <c r="W98" s="1"/>
       <c r="X98" s="2"/>
     </row>
-    <row r="99" spans="1:24" ht="60">
+    <row r="99" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>36</v>
@@ -5322,7 +5375,7 @@
         <v>34</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="P99" s="1"/>
       <c r="Q99" s="1"/>
@@ -5334,9 +5387,9 @@
       <c r="W99" s="1"/>
       <c r="X99" s="2"/>
     </row>
-    <row r="100" spans="1:24" ht="45">
+    <row r="100" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>40</v>
@@ -5364,15 +5417,15 @@
         <v>34</v>
       </c>
       <c r="U100" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="V100" s="1"/>
       <c r="W100" s="1"/>
       <c r="X100" s="2"/>
     </row>
-    <row r="101" spans="1:24" ht="60">
+    <row r="101" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>42</v>
@@ -5400,15 +5453,15 @@
         <v>52</v>
       </c>
       <c r="U101" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="V101" s="1"/>
       <c r="W101" s="1"/>
       <c r="X101" s="2"/>
     </row>
-    <row r="102" spans="1:24" ht="75">
+    <row r="102" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>44</v>
@@ -5433,18 +5486,18 @@
         <v>34</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="U102" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="V102" s="1"/>
       <c r="W102" s="1"/>
       <c r="X102" s="2"/>
     </row>
-    <row r="103" spans="1:24" ht="75">
+    <row r="103" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>47</v>
@@ -5469,18 +5522,18 @@
         <v>31</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="U103" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="V103" s="1"/>
       <c r="W103" s="1"/>
       <c r="X103" s="2"/>
     </row>
-    <row r="104" spans="1:24" ht="60">
+    <row r="104" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>51</v>
@@ -5508,15 +5561,15 @@
         <v>41</v>
       </c>
       <c r="U104" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="V104" s="1"/>
       <c r="W104" s="1"/>
       <c r="X104" s="2"/>
     </row>
-    <row r="105" spans="1:24" ht="75">
+    <row r="105" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>54</v>
@@ -5544,15 +5597,15 @@
         <v>49</v>
       </c>
       <c r="U105" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="V105" s="1"/>
       <c r="W105" s="1"/>
       <c r="X105" s="2"/>
     </row>
-    <row r="106" spans="1:24" ht="75">
+    <row r="106" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>57</v>
@@ -5580,18 +5633,18 @@
         <v>38</v>
       </c>
       <c r="U106" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="V106" s="1"/>
       <c r="W106" s="1"/>
       <c r="X106" s="2"/>
     </row>
-    <row r="107" spans="1:24" ht="60">
+    <row r="107" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>45</v>
@@ -5600,7 +5653,7 @@
         <v>52</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F107" s="1"/>
       <c r="G107" s="1"/>
@@ -5622,12 +5675,12 @@
       <c r="W107" s="1"/>
       <c r="X107" s="2"/>
     </row>
-    <row r="108" spans="1:24" ht="75">
+    <row r="108" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>41</v>
@@ -5636,7 +5689,7 @@
         <v>45</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
@@ -5658,12 +5711,12 @@
       <c r="W108" s="1"/>
       <c r="X108" s="2"/>
     </row>
-    <row r="109" spans="1:24" ht="60">
+    <row r="109" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
@@ -5685,7 +5738,7 @@
         <v>41</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S109" s="1"/>
       <c r="T109" s="1"/>
@@ -5694,12 +5747,12 @@
       <c r="W109" s="1"/>
       <c r="X109" s="2"/>
     </row>
-    <row r="110" spans="1:24" ht="75">
+    <row r="110" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
@@ -5721,7 +5774,7 @@
         <v>35</v>
       </c>
       <c r="R110" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="S110" s="1"/>
       <c r="T110" s="1"/>
@@ -5730,12 +5783,12 @@
       <c r="W110" s="1"/>
       <c r="X110" s="2"/>
     </row>
-    <row r="111" spans="1:24" ht="75">
+    <row r="111" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
@@ -5757,7 +5810,7 @@
         <v>31</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S111" s="1"/>
       <c r="T111" s="1"/>
@@ -5766,12 +5819,12 @@
       <c r="W111" s="1"/>
       <c r="X111" s="2"/>
     </row>
-    <row r="112" spans="1:24" ht="75">
+    <row r="112" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
@@ -5793,7 +5846,7 @@
         <v>52</v>
       </c>
       <c r="R112" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S112" s="1"/>
       <c r="T112" s="1"/>
@@ -5802,12 +5855,12 @@
       <c r="W112" s="1"/>
       <c r="X112" s="2"/>
     </row>
-    <row r="113" spans="1:24" ht="75">
+    <row r="113" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
@@ -5829,7 +5882,7 @@
         <v>34</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="S113" s="1"/>
       <c r="T113" s="1"/>
@@ -5838,12 +5891,12 @@
       <c r="W113" s="1"/>
       <c r="X113" s="2"/>
     </row>
-    <row r="114" spans="1:24" ht="45">
+    <row r="114" spans="1:24" ht="42" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
@@ -5865,7 +5918,7 @@
         <v>38</v>
       </c>
       <c r="R114" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="S114" s="1"/>
       <c r="T114" s="1"/>
@@ -5874,21 +5927,21 @@
       <c r="W114" s="1"/>
       <c r="X114" s="2"/>
     </row>
-    <row r="115" spans="1:24" ht="90">
+    <row r="115" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F115" s="1"/>
       <c r="G115" s="1"/>
@@ -5910,21 +5963,21 @@
       <c r="W115" s="1"/>
       <c r="X115" s="2"/>
     </row>
-    <row r="116" spans="1:24" ht="90">
+    <row r="116" spans="1:24" ht="84" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F116" s="1"/>
       <c r="G116" s="1"/>
@@ -5946,33 +5999,33 @@
       <c r="W116" s="1"/>
       <c r="X116" s="2"/>
     </row>
-    <row r="117" spans="1:24" ht="60">
+    <row r="117" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
       <c r="F117" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="I117" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J117" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>56</v>
@@ -5990,36 +6043,36 @@
       <c r="W117" s="1"/>
       <c r="X117" s="2"/>
     </row>
-    <row r="118" spans="1:24" ht="60">
+    <row r="118" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
       <c r="F118" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H118" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J118" s="1" t="s">
         <v>56</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M118" s="1"/>
       <c r="N118" s="1"/>
@@ -6034,12 +6087,12 @@
       <c r="W118" s="1"/>
       <c r="X118" s="2"/>
     </row>
-    <row r="119" spans="1:24" ht="60">
+    <row r="119" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
@@ -6049,16 +6102,16 @@
       </c>
       <c r="G119" s="1"/>
       <c r="H119" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L119" s="1"/>
       <c r="M119" s="1"/>
@@ -6074,12 +6127,12 @@
       <c r="W119" s="1"/>
       <c r="X119" s="2"/>
     </row>
-    <row r="120" spans="1:24" ht="60">
+    <row r="120" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
@@ -6089,16 +6142,16 @@
       </c>
       <c r="G120" s="1"/>
       <c r="H120" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J120" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="I120" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="K120" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L120" s="1"/>
       <c r="M120" s="1"/>
@@ -6114,9 +6167,9 @@
       <c r="W120" s="1"/>
       <c r="X120" s="2"/>
     </row>
-    <row r="121" spans="1:24" ht="75">
+    <row r="121" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>24</v>
@@ -6135,10 +6188,10 @@
         <v>45</v>
       </c>
       <c r="N121" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="O121" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1"/>
@@ -6150,9 +6203,9 @@
       <c r="W121" s="1"/>
       <c r="X121" s="2"/>
     </row>
-    <row r="122" spans="1:24" ht="60">
+    <row r="122" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>28</v>
@@ -6174,7 +6227,7 @@
         <v>38</v>
       </c>
       <c r="O122" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="1"/>
@@ -6186,9 +6239,9 @@
       <c r="W122" s="1"/>
       <c r="X122" s="2"/>
     </row>
-    <row r="123" spans="1:24" ht="75">
+    <row r="123" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>32</v>
@@ -6207,10 +6260,10 @@
         <v>52</v>
       </c>
       <c r="N123" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1"/>
@@ -6222,9 +6275,9 @@
       <c r="W123" s="1"/>
       <c r="X123" s="2"/>
     </row>
-    <row r="124" spans="1:24" ht="75">
+    <row r="124" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>36</v>
@@ -6243,10 +6296,10 @@
         <v>41</v>
       </c>
       <c r="N124" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="O124" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1"/>
@@ -6258,37 +6311,37 @@
       <c r="W124" s="1"/>
       <c r="X124" s="2"/>
     </row>
-    <row r="125" spans="1:24" ht="30">
+    <row r="125" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="I125" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K125" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>80</v>
       </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
@@ -6304,37 +6357,37 @@
       <c r="W125" s="1"/>
       <c r="X125" s="2"/>
     </row>
-    <row r="126" spans="1:24" ht="30">
+    <row r="126" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
+      </c>
+      <c r="F126" s="10" t="s">
+        <v>285</v>
       </c>
       <c r="G126" s="1"/>
       <c r="H126" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I126" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
+      </c>
+      <c r="J126" s="5" t="s">
+        <v>286</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
@@ -6350,9 +6403,9 @@
       <c r="W126" s="1"/>
       <c r="X126" s="2"/>
     </row>
-    <row r="127" spans="1:24" ht="75">
+    <row r="127" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>40</v>
@@ -6374,21 +6427,21 @@
       <c r="Q127" s="6"/>
       <c r="R127" s="6"/>
       <c r="S127" s="9" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="T127" s="9" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="U127" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="V127" s="1"/>
       <c r="W127" s="1"/>
       <c r="X127" s="2"/>
     </row>
-    <row r="128" spans="1:24" ht="75">
+    <row r="128" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>42</v>
@@ -6422,9 +6475,9 @@
       <c r="W128" s="1"/>
       <c r="X128" s="2"/>
     </row>
-    <row r="129" spans="1:24" ht="75">
+    <row r="129" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>44</v>
@@ -6452,15 +6505,15 @@
         <v>41</v>
       </c>
       <c r="U129" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V129" s="1"/>
       <c r="W129" s="1"/>
       <c r="X129" s="2"/>
     </row>
-    <row r="130" spans="1:24" ht="75">
+    <row r="130" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>47</v>
@@ -6488,15 +6541,15 @@
         <v>26</v>
       </c>
       <c r="U130" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="V130" s="1"/>
       <c r="W130" s="1"/>
       <c r="X130" s="2"/>
     </row>
-    <row r="131" spans="1:24" ht="105">
+    <row r="131" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>51</v>
@@ -6521,18 +6574,18 @@
         <v>26</v>
       </c>
       <c r="T131" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="U131" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="V131" s="1"/>
       <c r="W131" s="1"/>
       <c r="X131" s="2"/>
     </row>
-    <row r="132" spans="1:24" ht="75">
+    <row r="132" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>54</v>
@@ -6560,15 +6613,15 @@
         <v>38</v>
       </c>
       <c r="U132" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="V132" s="1"/>
       <c r="W132" s="1"/>
       <c r="X132" s="2"/>
     </row>
-    <row r="133" spans="1:24" ht="75">
+    <row r="133" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>57</v>
@@ -6593,30 +6646,30 @@
         <v>49</v>
       </c>
       <c r="T133" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="U133" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="V133" s="1"/>
       <c r="W133" s="1"/>
       <c r="X133" s="2"/>
     </row>
-    <row r="134" spans="1:24" ht="75">
+    <row r="134" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F134" s="1"/>
       <c r="G134" s="1"/>
@@ -6638,21 +6691,21 @@
       <c r="W134" s="1"/>
       <c r="X134" s="2"/>
     </row>
-    <row r="135" spans="1:24" ht="75">
+    <row r="135" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
@@ -6674,12 +6727,12 @@
       <c r="W135" s="1"/>
       <c r="X135" s="2"/>
     </row>
-    <row r="136" spans="1:24" ht="105">
+    <row r="136" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
@@ -6698,10 +6751,10 @@
         <v>45</v>
       </c>
       <c r="Q136" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="R136" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="R136" s="1" t="s">
-        <v>234</v>
       </c>
       <c r="S136" s="1"/>
       <c r="T136" s="1"/>
@@ -6710,12 +6763,12 @@
       <c r="W136" s="1"/>
       <c r="X136" s="2"/>
     </row>
-    <row r="137" spans="1:24" ht="75">
+    <row r="137" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
@@ -6734,10 +6787,10 @@
         <v>38</v>
       </c>
       <c r="Q137" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="R137" s="1" t="s">
-        <v>128</v>
+        <v>71</v>
+      </c>
+      <c r="R137" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="S137" s="1"/>
       <c r="T137" s="1"/>
@@ -6746,12 +6799,12 @@
       <c r="W137" s="1"/>
       <c r="X137" s="2"/>
     </row>
-    <row r="138" spans="1:24" ht="105">
+    <row r="138" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
@@ -6773,7 +6826,7 @@
         <v>26</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="S138" s="1"/>
       <c r="T138" s="1"/>
@@ -6782,12 +6835,12 @@
       <c r="W138" s="1"/>
       <c r="X138" s="2"/>
     </row>
-    <row r="139" spans="1:24" ht="75">
+    <row r="139" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
@@ -6806,10 +6859,10 @@
         <v>26</v>
       </c>
       <c r="Q139" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
@@ -6818,12 +6871,12 @@
       <c r="W139" s="1"/>
       <c r="X139" s="2"/>
     </row>
-    <row r="140" spans="1:24" ht="75">
+    <row r="140" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
@@ -6845,7 +6898,7 @@
         <v>49</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="S140" s="1"/>
       <c r="T140" s="1"/>
@@ -6854,12 +6907,12 @@
       <c r="W140" s="1"/>
       <c r="X140" s="2"/>
     </row>
-    <row r="141" spans="1:24" ht="75">
+    <row r="141" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
@@ -6878,10 +6931,10 @@
         <v>49</v>
       </c>
       <c r="Q141" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="R141" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S141" s="1"/>
       <c r="T141" s="1"/>
@@ -6890,12 +6943,12 @@
       <c r="W141" s="1"/>
       <c r="X141" s="2"/>
     </row>
-    <row r="142" spans="1:24" ht="75">
+    <row r="142" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
@@ -6910,13 +6963,13 @@
         <v>26</v>
       </c>
       <c r="M142" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="O142" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1"/>
@@ -6928,12 +6981,12 @@
       <c r="W142" s="1"/>
       <c r="X142" s="2"/>
     </row>
-    <row r="143" spans="1:24" ht="75">
+    <row r="143" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
@@ -6948,13 +7001,13 @@
         <v>41</v>
       </c>
       <c r="M143" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O143" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1"/>
@@ -6966,12 +7019,12 @@
       <c r="W143" s="1"/>
       <c r="X143" s="2"/>
     </row>
-    <row r="144" spans="1:24" ht="75">
+    <row r="144" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
@@ -6989,10 +7042,10 @@
         <v>26</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="O144" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="P144" s="1"/>
       <c r="Q144" s="1"/>
@@ -7004,37 +7057,37 @@
       <c r="W144" s="1"/>
       <c r="X144" s="2"/>
     </row>
-    <row r="145" spans="1:24" ht="60">
+    <row r="145" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C145" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E145" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>56</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I145" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="K145" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="J145" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K145" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
@@ -7050,12 +7103,12 @@
       <c r="W145" s="1"/>
       <c r="X145" s="2"/>
     </row>
-    <row r="146" spans="1:24" ht="60">
+    <row r="146" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
@@ -7065,19 +7118,19 @@
       </c>
       <c r="G146" s="1"/>
       <c r="H146" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="K146" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I146" s="1" t="s">
+      <c r="L146" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="J146" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="K146" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="L146" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
@@ -7092,12 +7145,12 @@
       <c r="W146" s="1"/>
       <c r="X146" s="2"/>
     </row>
-    <row r="147" spans="1:24" ht="60">
+    <row r="147" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
@@ -7107,19 +7160,19 @@
       </c>
       <c r="G147" s="1"/>
       <c r="H147" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I147" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K147" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J147" s="1" t="s">
+      <c r="L147" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="K147" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L147" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="M147" s="1"/>
       <c r="N147" s="1"/>
@@ -7134,38 +7187,38 @@
       <c r="W147" s="1"/>
       <c r="X147" s="2"/>
     </row>
-    <row r="148" spans="1:24" ht="60">
+    <row r="148" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G148" s="1"/>
       <c r="H148" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I148" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J148" s="1"/>
       <c r="K148" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L148" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M148" s="1"/>
       <c r="N148" s="1"/>
@@ -7180,37 +7233,37 @@
       <c r="W148" s="1"/>
       <c r="X148" s="2"/>
     </row>
-    <row r="149" spans="1:24" ht="60">
+    <row r="149" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G149" s="1"/>
       <c r="H149" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K149" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L149" s="1"/>
       <c r="M149" s="1"/>
@@ -7226,12 +7279,12 @@
       <c r="W149" s="1"/>
       <c r="X149" s="2"/>
     </row>
-    <row r="150" spans="1:24" ht="15">
+    <row r="150" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
@@ -7242,7 +7295,7 @@
       <c r="I150" s="1"/>
       <c r="J150" s="1"/>
       <c r="K150" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
@@ -7258,12 +7311,12 @@
       <c r="W150" s="1"/>
       <c r="X150" s="2"/>
     </row>
-    <row r="151" spans="1:24" ht="15">
+    <row r="151" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
@@ -7274,7 +7327,7 @@
       <c r="I151" s="1"/>
       <c r="J151" s="1"/>
       <c r="K151" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
@@ -7290,9 +7343,9 @@
       <c r="W151" s="1"/>
       <c r="X151" s="2"/>
     </row>
-    <row r="152" spans="1:24" ht="75">
+    <row r="152" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>24</v>
@@ -7314,7 +7367,7 @@
         <v>34</v>
       </c>
       <c r="O152" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="P152" s="1"/>
       <c r="Q152" s="1"/>
@@ -7326,9 +7379,9 @@
       <c r="W152" s="1"/>
       <c r="X152" s="2"/>
     </row>
-    <row r="153" spans="1:24" ht="75">
+    <row r="153" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>28</v>
@@ -7350,7 +7403,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="P153" s="1"/>
       <c r="Q153" s="1"/>
@@ -7362,9 +7415,9 @@
       <c r="W153" s="1"/>
       <c r="X153" s="2"/>
     </row>
-    <row r="154" spans="1:24" ht="75">
+    <row r="154" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>32</v>
@@ -7385,8 +7438,8 @@
       <c r="N154" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O154" s="1" t="s">
-        <v>217</v>
+      <c r="O154" s="5" t="s">
+        <v>283</v>
       </c>
       <c r="P154" s="1"/>
       <c r="Q154" s="1"/>
@@ -7398,9 +7451,9 @@
       <c r="W154" s="1"/>
       <c r="X154" s="2"/>
     </row>
-    <row r="155" spans="1:24" ht="75">
+    <row r="155" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>36</v>
@@ -7421,8 +7474,8 @@
       <c r="N155" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O155" s="1" t="s">
-        <v>217</v>
+      <c r="O155" s="5" t="s">
+        <v>284</v>
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1"/>
@@ -7434,38 +7487,38 @@
       <c r="W155" s="1"/>
       <c r="X155" s="2"/>
     </row>
-    <row r="156" spans="1:24" ht="30">
+    <row r="156" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F156" s="1"/>
       <c r="G156" s="1"/>
       <c r="H156" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="I156" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M156" s="1"/>
       <c r="N156" s="1"/>
@@ -7480,38 +7533,38 @@
       <c r="W156" s="1"/>
       <c r="X156" s="2"/>
     </row>
-    <row r="157" spans="1:24" ht="30">
+    <row r="157" spans="1:24" ht="28" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F157" s="1"/>
       <c r="G157" s="1"/>
       <c r="H157" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J157" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="K157" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="L157" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="K157" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="L157" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="M157" s="1"/>
       <c r="N157" s="1"/>
@@ -7526,9 +7579,9 @@
       <c r="W157" s="1"/>
       <c r="X157" s="2"/>
     </row>
-    <row r="158" spans="1:24" ht="75">
+    <row r="158" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>40</v>
@@ -7550,21 +7603,21 @@
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
       <c r="S158" s="9" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="T158" s="9" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="U158" s="7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="V158" s="1"/>
       <c r="W158" s="1"/>
       <c r="X158" s="2"/>
     </row>
-    <row r="159" spans="1:24" ht="75">
+    <row r="159" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>42</v>
@@ -7589,18 +7642,18 @@
         <v>49</v>
       </c>
       <c r="T159" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="U159" s="1" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="V159" s="1"/>
       <c r="W159" s="1"/>
       <c r="X159" s="2"/>
     </row>
-    <row r="160" spans="1:24" ht="75">
+    <row r="160" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>44</v>
@@ -7625,18 +7678,18 @@
         <v>52</v>
       </c>
       <c r="T160" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="U160" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="V160" s="1"/>
       <c r="W160" s="1"/>
       <c r="X160" s="2"/>
     </row>
-    <row r="161" spans="1:24" ht="75">
+    <row r="161" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>47</v>
@@ -7664,15 +7717,15 @@
         <v>41</v>
       </c>
       <c r="U161" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="V161" s="1"/>
       <c r="W161" s="1"/>
       <c r="X161" s="2"/>
     </row>
-    <row r="162" spans="1:24" ht="75">
+    <row r="162" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -7697,18 +7750,18 @@
         <v>38</v>
       </c>
       <c r="T162" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="U162" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="V162" s="1"/>
       <c r="W162" s="1"/>
       <c r="X162" s="2"/>
     </row>
-    <row r="163" spans="1:24" ht="75">
+    <row r="163" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>54</v>
@@ -7730,21 +7783,21 @@
       <c r="Q163" s="1"/>
       <c r="R163" s="1"/>
       <c r="S163" s="5" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="T163" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U163" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="V163" s="1"/>
       <c r="W163" s="1"/>
       <c r="X163" s="2"/>
     </row>
-    <row r="164" spans="1:24" ht="75">
+    <row r="164" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>57</v>
@@ -7769,30 +7822,30 @@
         <v>45</v>
       </c>
       <c r="T164" s="5" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="U164" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="V164" s="1"/>
       <c r="W164" s="1"/>
       <c r="X164" s="2"/>
     </row>
-    <row r="165" spans="1:24" ht="105">
+    <row r="165" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="E165" s="1" t="s">
-        <v>262</v>
+        <v>257</v>
+      </c>
+      <c r="E165" s="5" t="s">
+        <v>280</v>
       </c>
       <c r="F165" s="1"/>
       <c r="G165" s="1"/>
@@ -7814,21 +7867,21 @@
       <c r="W165" s="1"/>
       <c r="X165" s="2"/>
     </row>
-    <row r="166" spans="1:24" ht="105">
+    <row r="166" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>262</v>
+        <v>214</v>
+      </c>
+      <c r="E166" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="F166" s="1"/>
       <c r="G166" s="1"/>
@@ -7850,12 +7903,12 @@
       <c r="W166" s="1"/>
       <c r="X166" s="2"/>
     </row>
-    <row r="167" spans="1:24" ht="75">
+    <row r="167" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
@@ -7874,10 +7927,10 @@
         <v>49</v>
       </c>
       <c r="Q167" s="1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S167" s="1"/>
       <c r="T167" s="1"/>
@@ -7886,12 +7939,12 @@
       <c r="W167" s="1"/>
       <c r="X167" s="2"/>
     </row>
-    <row r="168" spans="1:24" ht="75">
+    <row r="168" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
@@ -7922,12 +7975,12 @@
       <c r="W168" s="1"/>
       <c r="X168" s="2"/>
     </row>
-    <row r="169" spans="1:24" ht="75">
+    <row r="169" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
@@ -7946,10 +7999,10 @@
         <v>38</v>
       </c>
       <c r="Q169" s="1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="S169" s="1"/>
       <c r="T169" s="1"/>
@@ -7958,12 +8011,12 @@
       <c r="W169" s="1"/>
       <c r="X169" s="2"/>
     </row>
-    <row r="170" spans="1:24" ht="90">
+    <row r="170" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
@@ -7984,8 +8037,8 @@
       <c r="Q170" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="R170" s="1" t="s">
-        <v>265</v>
+      <c r="R170" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="S170" s="1"/>
       <c r="T170" s="1"/>
@@ -7994,12 +8047,12 @@
       <c r="W170" s="1"/>
       <c r="X170" s="2"/>
     </row>
-    <row r="171" spans="1:24" ht="105">
+    <row r="171" spans="1:24" ht="98" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
@@ -8018,10 +8071,10 @@
         <v>26</v>
       </c>
       <c r="Q171" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="R171" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="S171" s="1"/>
       <c r="T171" s="1"/>
@@ -8030,12 +8083,12 @@
       <c r="W171" s="1"/>
       <c r="X171" s="2"/>
     </row>
-    <row r="172" spans="1:24" ht="75">
+    <row r="172" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
@@ -8054,10 +8107,10 @@
         <v>34</v>
       </c>
       <c r="Q172" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="S172" s="1"/>
       <c r="T172" s="1"/>
@@ -8066,12 +8119,12 @@
       <c r="W172" s="1"/>
       <c r="X172" s="2"/>
     </row>
-    <row r="173" spans="1:24" ht="75">
+    <row r="173" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>29</v>
@@ -8097,14 +8150,14 @@
         <v>45</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M173" s="1"/>
       <c r="N173" s="1" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="O173" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1"/>
@@ -8116,15 +8169,15 @@
       <c r="W173" s="1"/>
       <c r="X173" s="2"/>
     </row>
-    <row r="174" spans="1:24" ht="75">
+    <row r="174" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>52</v>
@@ -8147,14 +8200,14 @@
         <v>38</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="M174" s="1"/>
       <c r="N174" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O174" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1"/>
@@ -8166,15 +8219,15 @@
       <c r="W174" s="1"/>
       <c r="X174" s="2"/>
     </row>
-    <row r="175" spans="1:24" ht="75">
+    <row r="175" spans="1:24" ht="70" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>45</v>
@@ -8197,11 +8250,11 @@
         <v>41</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="M175" s="1"/>
       <c r="N175" s="1" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="O175" s="1"/>
       <c r="P175" s="1"/>
@@ -8214,12 +8267,12 @@
       <c r="W175" s="1"/>
       <c r="X175" s="2"/>
     </row>
-    <row r="176" spans="1:24" ht="60">
+    <row r="176" spans="1:24" ht="56" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
@@ -8227,13 +8280,13 @@
       <c r="F176" s="1"/>
       <c r="G176" s="1"/>
       <c r="H176" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
@@ -8250,12 +8303,12 @@
       <c r="W176" s="1"/>
       <c r="X176" s="2"/>
     </row>
-    <row r="177" spans="1:24" ht="15">
+    <row r="177" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
@@ -8263,13 +8316,13 @@
       <c r="F177" s="1"/>
       <c r="G177" s="1"/>
       <c r="H177" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I177" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J177" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="I177" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J177" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="K177" s="1"/>
       <c r="L177" s="1"/>
@@ -8287,8 +8340,9 @@
       <c r="X177" s="2"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W177" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>